--- a/data/output/workbook/2026-07-17.xlsx
+++ b/data/output/workbook/2026-07-17.xlsx
@@ -582,7 +582,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10687050"/>
+    <ext cx="10125075" cy="10287000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -612,7 +612,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10420350"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17 20:00</t>
+          <t>2026-07-17 23:00</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6792,171 +6792,329 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles offense vs Houston Astros defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles offense vs Houston Astros defense</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>4.612</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H68" s="34" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J68" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>5.023</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>8.208</v>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>7.625</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.612</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>5.2</v>
+        <v>1.271</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>5.023</v>
+        <v>1.292</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.208</v>
+        <v>8.917</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -7020,396 +7178,396 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.625</v>
+        <v>8.417</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.271</v>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.488</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J72" s="33" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>0.733</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.292</v>
+        <v>0.643</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>8.917</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>8.417</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>Houston Astros offense vs Baltimore Orioles defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C75" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D75" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E75" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F75" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G75" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H75" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J75" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K75" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L75" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M75" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N75" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O75" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P75" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q75" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Houston Astros offense vs Baltimore Orioles defense</t>
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>4.919</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J76" s="33" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>4.718</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>8.083</v>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>8.833</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.919</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.567</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>4</v>
+        <v>1.417</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.718</v>
+        <v>1.062</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.083</v>
+        <v>7.729</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -7473,226 +7631,68 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.833</v>
+        <v>8</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>1.417</v>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.679</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F80" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>0.633</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.062</v>
+        <v>0.452</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>7.729</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7711,7 +7711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7728,907 +7728,907 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>San Diego Padres offense vs Kansas City Royals defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H68" s="34" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J68" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>5.322</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>7.087</v>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>8.603999999999999</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>1.022</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.348000000000001</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.033</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>6.333</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.208</v>
+        <v>5.322</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>7.087</v>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>8.603999999999999</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8.348000000000001</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.208</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.422</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H72" s="34" t="inlineStr">
+      <c r="H75" s="34" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J72" s="33" t="inlineStr">
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.85</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.798</v>
       </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Kansas City Royals offense vs San Diego Padres defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>4.253</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H76" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>6.133</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>4.256</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>7.848</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>0.896</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.021000000000001</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.253</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H79" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>6.133</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>5.2</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.304</v>
+        <v>4.256</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>7.848</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>8.021000000000001</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>8.304</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.524</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="D80" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="E80" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="F80" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H80" s="33" t="inlineStr">
+      <c r="H83" s="33" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="33" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="33" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="K80" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L80" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M80" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="N80" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="O80" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P80" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.494</v>
       </c>
-      <c r="Q80" s="35" t="inlineStr">
+      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -9801,13 +9801,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.6817</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-252</v>
+        <v>-214</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 71.6% (fair -252). Your call.</t>
+          <t>Model 68.2% (fair -214). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9939,7 +9939,7 @@
         <v>-192</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9999,10 +9999,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6463</v>
+        <v>0.6406000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-183</v>
+        <v>-178</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>178</v>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -183). Your call.</t>
+          <t>Model 64.1% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6537999999999999</v>
+        <v>0.6529</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-189</v>
+        <v>-188</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 65.4% (fair -189). Your call.</t>
+          <t>Model 65.3% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10107,17 +10107,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -10127,14 +10127,14 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays +1.5</t>
+          <t>Texas Rangers +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5984</v>
+        <v>0.6196999999999999</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-149</v>
+        <v>-163</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>170</v>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10173,37 +10173,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Seattle Mariners</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Tampa Bay Rays +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-282</v>
+        <v>-148</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 73.8% (fair -282). Your call.</t>
+          <t>Model 59.6% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10239,37 +10239,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>San Francisco Giants @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays +1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5928</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-146</v>
+        <v>-282</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 73.8% (fair -282). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10305,7 +10305,7 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -10329,10 +10329,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5759000000000001</v>
+        <v>0.5922000000000001</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-136</v>
+        <v>-145</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>170</v>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10371,17 +10371,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -10391,14 +10391,14 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles +1.5</t>
+          <t>Tampa Bay Rays +1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5801000000000001</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-134</v>
+        <v>-138</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>170</v>
@@ -10425,7 +10425,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10442,12 +10442,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -10457,17 +10457,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies -1.5</t>
+          <t>Baltimore Orioles +1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5579</v>
+        <v>0.5712999999999999</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-126</v>
+        <v>-133</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10503,17 +10503,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Toronto Blue Jays</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -10523,17 +10523,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5681</v>
+        <v>0.4125</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-132</v>
+        <v>142</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>144</v>
+        <v>270</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -132). Your call.</t>
+          <t>Model 41.2% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -10574,32 +10574,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Cincinnati Reds @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Colorado Rockies -1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5564</v>
+        <v>0.5643</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-125</v>
+        <v>-130</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 56.4% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10635,17 +10635,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -10659,13 +10659,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5956</v>
+        <v>0.5711999999999999</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-147</v>
+        <v>-133</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -147). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10701,17 +10701,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>Chicago White Sox @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -10721,17 +10721,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5875</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-142</v>
+        <v>-131</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10755,7 +10755,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -142). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10772,12 +10772,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Arizona Diamondbacks</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -10787,17 +10787,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5843</v>
+        <v>0.3722</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-141</v>
+        <v>169</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>117</v>
+        <v>270</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -141). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10833,17 +10833,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>St. Louis Cardinals @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -10857,13 +10857,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5145</v>
+        <v>0.6214</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-106</v>
+        <v>-164</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10899,12 +10899,12 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -10919,17 +10919,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5768</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-136</v>
+        <v>-111</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10989,10 +10989,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5782</v>
+        <v>0.5907</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-137</v>
+        <v>-144</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>113</v>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 59.1% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11036,32 +11036,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5635</v>
+        <v>0.5843</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-129</v>
+        <v>-141</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 58.4% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11127,7 +11127,7 @@
         <v>-142</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11187,13 +11187,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5725</v>
+        <v>0.578</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-134</v>
+        <v>-137</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11229,37 +11229,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Indiana Fever</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Houston Astros -1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.4287</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-113</v>
+        <v>133</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11295,37 +11295,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Portland Fire @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros -1.5</t>
+          <t>Over 175.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4279</v>
+        <v>0.555</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>134</v>
+        <v>-125</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11361,17 +11361,17 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>New York Liberty @ Indiana Fever</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -11381,17 +11381,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5921</v>
+        <v>0.5314</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-145</v>
+        <v>-113</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-106</v>
+        <v>117</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11724,10 +11724,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4436</v>
+        <v>0.4288</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>130</v>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -11790,10 +11790,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5564</v>
+        <v>0.5711999999999999</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-125</v>
+        <v>-133</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>144</v>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -11856,10 +11856,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4016</v>
+        <v>0.4037</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 40.4% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -11922,10 +11922,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5984</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-149</v>
+        <v>-148</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>170</v>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 59.6% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4855</v>
+        <v>0.4733</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>130</v>
@@ -12150,7 +12150,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -12186,10 +12186,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5145</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-106</v>
+        <v>-111</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>144</v>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -12252,10 +12252,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4072</v>
+        <v>0.4078</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>178</v>
@@ -12282,7 +12282,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -12318,10 +12318,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5928</v>
+        <v>0.5922000000000001</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-146</v>
+        <v>-145</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>170</v>
@@ -12348,7 +12348,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.502</v>
+        <v>0.4776</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-101</v>
+        <v>109</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>117</v>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -12582,10 +12582,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.498</v>
+        <v>0.5224</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>101</v>
+        <v>-109</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>108</v>
@@ -12612,7 +12612,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -12648,7 +12648,7 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.631</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>-171</v>
@@ -12678,7 +12678,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 63.0% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.369</v>
+        <v>0.3695000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>171</v>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 37.0% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -12780,10 +12780,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.3587399999999999</v>
+        <v>0.2871144000000002</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>208</v>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 35.9% (fair +179). Your call.</t>
+          <t>Model 28.7% (fair +248). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -12846,10 +12846,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.6412600000000001</v>
+        <v>0.7128855999999998</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-179</v>
+        <v>-248</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>-130</v>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -179). Your call.</t>
+          <t>Model 71.3% (fair -248). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -12912,10 +12912,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4863</v>
+        <v>0.4885</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>117</v>
@@ -12942,7 +12942,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12978,10 +12978,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5137</v>
+        <v>0.5115000000000001</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>105</v>
@@ -13008,7 +13008,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -13044,10 +13044,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4701</v>
+        <v>0.4733</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>105</v>
@@ -13074,7 +13074,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -13110,10 +13110,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5299</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-108</v>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -13176,7 +13176,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4462</v>
+        <v>0.4464</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>124</v>
@@ -13242,7 +13242,7 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5538</v>
+        <v>0.5536</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>-124</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4319</v>
+        <v>0.433</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>130</v>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +132). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -13374,10 +13374,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5681</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-132</v>
+        <v>-131</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>144</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -132). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -13440,10 +13440,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3537</v>
+        <v>0.3594</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>163</v>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 35.4% (fair +183). Your call.</t>
+          <t>Model 35.9% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -13506,10 +13506,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6463</v>
+        <v>0.6406000000000001</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-183</v>
+        <v>-178</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>178</v>
@@ -13536,7 +13536,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -183). Your call.</t>
+          <t>Model 64.1% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -14172,7 +14172,7 @@
         <v>-142</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -14496,13 +14496,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5213</v>
+        <v>0.5229</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -14562,13 +14562,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.3922</v>
+        <v>0.3906999999999999</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -14628,10 +14628,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4279</v>
+        <v>0.4287</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>170</v>
@@ -14658,7 +14658,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -14694,10 +14694,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5712999999999999</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-134</v>
+        <v>-133</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>170</v>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -14760,10 +14760,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.5257000000000001</v>
+        <v>0.5247999999999999</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="H53" s="15" t="n">
         <v>-113</v>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -14826,10 +14826,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.4743</v>
+        <v>0.4752</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H54" s="15" t="n">
         <v>113</v>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -14892,13 +14892,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4218</v>
+        <v>0.4093</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -14922,7 +14922,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 40.9% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -14958,10 +14958,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5782</v>
+        <v>0.5907</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-137</v>
+        <v>-144</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>113</v>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 59.1% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -15024,10 +15024,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.5728</v>
+        <v>0.5764</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>-134</v>
+        <v>-136</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>-138</v>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -15090,13 +15090,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.4272</v>
+        <v>0.4236</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -15288,10 +15288,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4304</v>
+        <v>0.4487</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>113</v>
@@ -15318,7 +15318,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +132). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -15354,13 +15354,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5696</v>
+        <v>0.5513</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-132</v>
+        <v>-123</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-102</v>
+        <v>105</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -132). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -15420,10 +15420,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5579</v>
+        <v>0.5643</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-126</v>
+        <v>-130</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>160</v>
@@ -15450,7 +15450,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 56.4% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -15486,10 +15486,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4421</v>
+        <v>0.4357</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>150</v>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 43.6% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -15552,10 +15552,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.5232</v>
+        <v>0.519</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -15580,7 +15580,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -15616,10 +15616,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.4768</v>
+        <v>0.4811</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -16192,13 +16192,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.45495</v>
+        <v>0.4550999999999999</v>
       </c>
       <c r="G75" s="14" t="n">
         <v>120</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -16258,13 +16258,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.54505</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="G76" s="14" t="n">
         <v>-120</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-114</v>
+        <v>-117</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -16330,7 +16330,7 @@
         <v>-142</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>117</v>
+        <v>19900</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -16396,7 +16396,7 @@
         <v>142</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -16528,7 +16528,7 @@
         <v>-192</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -16588,13 +16588,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5510368</v>
+        <v>0.4752</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-123</v>
+        <v>110</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -16654,13 +16654,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4489632</v>
+        <v>0.5248</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>123</v>
+        <v>-110</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-114</v>
+        <v>-117</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -16720,13 +16720,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.5768</v>
+        <v>0.6278</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-136</v>
+        <v>-169</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>117</v>
+        <v>19900</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -16786,13 +16786,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.4232</v>
+        <v>0.3722</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -16816,7 +16816,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -16852,10 +16852,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.2838</v>
+        <v>0.3183</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>252</v>
+        <v>214</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>178</v>
@@ -16882,7 +16882,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 28.4% (fair +252). Your call.</t>
+          <t>Model 31.8% (fair +214). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -16918,13 +16918,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.6817</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-252</v>
+        <v>-214</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 71.6% (fair -252). Your call.</t>
+          <t>Model 68.2% (fair -214). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -17122,7 +17122,7 @@
         <v>-106</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -17188,7 +17188,7 @@
         <v>106</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -17248,13 +17248,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.3942</v>
+        <v>0.3962</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -17278,7 +17278,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 39.6% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -17314,13 +17314,13 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.6058</v>
+        <v>0.6038</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-154</v>
+        <v>-152</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-162</v>
+        <v>-160</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 60.4% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -17380,13 +17380,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5231</v>
+        <v>0.5262</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -17446,10 +17446,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.4769</v>
+        <v>0.4738</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>104</v>
@@ -17476,7 +17476,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -17512,10 +17512,10 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.5144</v>
+        <v>0.5222</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-106</v>
+        <v>-109</v>
       </c>
       <c r="H95" s="15" t="n">
         <v>100</v>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -17578,13 +17578,13 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4856</v>
+        <v>0.4778</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -17608,7 +17608,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -17644,13 +17644,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.5863</v>
+        <v>0.5807</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-142</v>
+        <v>-138</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>-165</v>
+        <v>-156</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 58.1% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -17710,13 +17710,13 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4137</v>
+        <v>0.4193</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 41.9% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -17776,13 +17776,13 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.4365</v>
+        <v>0.4624</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -17806,7 +17806,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -17842,13 +17842,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.5635</v>
+        <v>0.5376</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-129</v>
+        <v>-116</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -17872,7 +17872,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -17908,13 +17908,13 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4728</v>
+        <v>0.4723</v>
       </c>
       <c r="G101" s="14" t="n">
         <v>112</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>-114</v>
+        <v>-110</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5272</v>
+        <v>0.5277000000000001</v>
       </c>
       <c r="G102" s="14" t="n">
         <v>-112</v>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -18040,13 +18040,13 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.6273</v>
+        <v>0.6256</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-168</v>
+        <v>-167</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>-155</v>
+        <v>-152</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -18070,7 +18070,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 62.7% (fair -168). Your call.</t>
+          <t>Model 62.6% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -18106,13 +18106,13 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.3727</v>
+        <v>0.3744</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -18136,7 +18136,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 37.3% (fair +168). Your call.</t>
+          <t>Model 37.4% (fair +167). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -18304,10 +18304,10 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5298</v>
+        <v>0.5238</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-113</v>
+        <v>-110</v>
       </c>
       <c r="H107" s="15" t="n">
         <v>-113</v>
@@ -18334,7 +18334,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -18370,10 +18370,10 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4702</v>
+        <v>0.4762</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H108" s="15" t="n">
         <v>108</v>
@@ -18400,7 +18400,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -18436,10 +18436,10 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.4387</v>
+        <v>0.44</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H109" s="15" t="n">
         <v>133</v>
@@ -18466,7 +18466,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -18502,10 +18502,10 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.5613</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-128</v>
+        <v>-127</v>
       </c>
       <c r="H110" s="15" t="n">
         <v>-138</v>
@@ -18532,7 +18532,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -18568,10 +18568,10 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.4883</v>
+        <v>0.4899</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H111" s="15" t="n">
         <v>104</v>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -18634,13 +18634,13 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.5117</v>
+        <v>0.5101</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -18664,7 +18664,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -18700,13 +18700,13 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.5248</v>
+        <v>0.5216</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>-110</v>
+        <v>-109</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -18766,10 +18766,10 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4752</v>
+        <v>0.4784</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H114" s="15" t="n">
         <v>100</v>
@@ -18796,7 +18796,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -18964,10 +18964,10 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.4878</v>
+        <v>0.4847</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H117" s="15" t="n">
         <v>100</v>
@@ -18994,7 +18994,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -19030,13 +19030,13 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5153</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -19060,7 +19060,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -19096,13 +19096,13 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.5008</v>
+        <v>0.49</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>-100</v>
+        <v>104</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>-110</v>
+        <v>104</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -19126,7 +19126,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -19162,10 +19162,10 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.4992</v>
+        <v>0.51</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="H120" s="15" t="n">
         <v>-104</v>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -19228,13 +19228,13 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.611</v>
+        <v>0.5989</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>-157</v>
+        <v>-149</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>-170</v>
+        <v>-155</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -19258,7 +19258,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -19294,13 +19294,13 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.389</v>
+        <v>0.4011</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -19324,7 +19324,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -19360,10 +19360,10 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.4648</v>
+        <v>0.4611</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H123" s="15" t="n">
         <v>117</v>
@@ -19390,7 +19390,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -19426,13 +19426,13 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.5352</v>
+        <v>0.5389</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>-115</v>
+        <v>-117</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>-108</v>
+        <v>-113</v>
       </c>
       <c r="I124" s="13">
         <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
@@ -19456,7 +19456,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -19492,10 +19492,10 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.4157</v>
+        <v>0.3786</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="H125" s="15" t="n">
         <v>133</v>
@@ -19522,7 +19522,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +141). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -19558,10 +19558,10 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.5843</v>
+        <v>0.6214</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-141</v>
+        <v>-164</v>
       </c>
       <c r="H126" s="15" t="n">
         <v>117</v>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -141). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -19624,13 +19624,13 @@
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.3462</v>
+        <v>0.3471</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H127" s="15" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
@@ -19654,7 +19654,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 34.6% (fair +189). Your call.</t>
+          <t>Model 34.7% (fair +188). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -19690,13 +19690,13 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.6537999999999999</v>
+        <v>0.6529</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-189</v>
+        <v>-188</v>
       </c>
       <c r="H128" s="15" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 65.4% (fair -189). Your call.</t>
+          <t>Model 65.3% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -19756,10 +19756,10 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.4655</v>
+        <v>0.4623</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H129" s="15" t="n">
         <v>108</v>
@@ -19786,7 +19786,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -19822,13 +19822,13 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.5345</v>
+        <v>0.5377</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -19888,10 +19888,10 @@
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.5178</v>
+        <v>0.5214</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>-107</v>
+        <v>-109</v>
       </c>
       <c r="H131" s="15" t="n">
         <v>100</v>
@@ -19918,7 +19918,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -19954,13 +19954,13 @@
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.4822</v>
+        <v>0.4786</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H132" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -20020,13 +20020,13 @@
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.4241</v>
+        <v>0.4199</v>
       </c>
       <c r="G133" s="14" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H133" s="15" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I133" s="13">
         <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
@@ -20050,7 +20050,7 @@
       </c>
       <c r="N133" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O133" s="15" t="n"/>
@@ -20086,10 +20086,10 @@
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.5759000000000001</v>
+        <v>0.5801000000000001</v>
       </c>
       <c r="G134" s="14" t="n">
-        <v>-136</v>
+        <v>-138</v>
       </c>
       <c r="H134" s="15" t="n">
         <v>170</v>
@@ -20116,7 +20116,7 @@
       </c>
       <c r="N134" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O134" s="15" t="n"/>
@@ -20152,10 +20152,10 @@
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.4681</v>
+        <v>0.4635</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H135" s="15" t="n">
         <v>108</v>
@@ -20182,7 +20182,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -20218,13 +20218,13 @@
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.5319</v>
+        <v>0.5365</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-114</v>
+        <v>-116</v>
       </c>
       <c r="H136" s="15" t="n">
-        <v>-111</v>
+        <v>-107</v>
       </c>
       <c r="I136" s="13">
         <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
@@ -20248,7 +20248,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -20284,10 +20284,10 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.4044</v>
+        <v>0.4157</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="H137" s="15" t="n">
         <v>122</v>
@@ -20314,7 +20314,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +147). Your call.</t>
+          <t>Model 41.6% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -20350,10 +20350,10 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.5956</v>
+        <v>0.5843</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>-147</v>
+        <v>-141</v>
       </c>
       <c r="H138" s="15" t="n">
         <v>115</v>
@@ -20380,7 +20380,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -147). Your call.</t>
+          <t>Model 58.4% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -20412,17 +20412,17 @@
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves +1.5</t>
+          <t>Atlanta Braves -1.5</t>
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.6329</v>
+        <v>0.3803</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>-172</v>
+        <v>163</v>
       </c>
       <c r="H139" s="15" t="n">
-        <v>-178</v>
+        <v>170</v>
       </c>
       <c r="I139" s="13">
         <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -172). Your call.</t>
+          <t>Model 38.0% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -20478,14 +20478,14 @@
       </c>
       <c r="E140" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers -1.5</t>
+          <t>Texas Rangers +1.5</t>
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.3671</v>
+        <v>0.6196999999999999</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>172</v>
+        <v>-163</v>
       </c>
       <c r="H140" s="15" t="n">
         <v>170</v>
@@ -20512,7 +20512,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 36.7% (fair +172). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -20548,7 +20548,7 @@
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.519</v>
+        <v>0.5184</v>
       </c>
       <c r="G141" s="14" t="n">
         <v>-108</v>
@@ -20576,7 +20576,7 @@
       </c>
       <c r="N141" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O141" s="15" t="n"/>
@@ -20612,7 +20612,7 @@
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.481</v>
+        <v>0.4816</v>
       </c>
       <c r="G142" s="14" t="n">
         <v>108</v>
@@ -20640,7 +20640,7 @@
       </c>
       <c r="N142" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O142" s="15" t="n"/>
@@ -20936,10 +20936,10 @@
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>0.4832</v>
+        <v>0.4892</v>
       </c>
       <c r="G147" s="14" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H147" s="15" t="n"/>
       <c r="I147" s="13">
@@ -20964,7 +20964,7 @@
       </c>
       <c r="N147" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O147" s="15" t="n"/>
@@ -21000,10 +21000,10 @@
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.5168</v>
+        <v>0.5108</v>
       </c>
       <c r="G148" s="14" t="n">
-        <v>-107</v>
+        <v>-104</v>
       </c>
       <c r="H148" s="15" t="n"/>
       <c r="I148" s="13">
@@ -21028,7 +21028,7 @@
       </c>
       <c r="N148" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O148" s="15" t="n"/>
@@ -21317,7 +21317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -21442,12 +21442,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Indiana Fever</t>
+          <t>Connecticut Sun @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -21457,17 +21457,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Connecticut Sun</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.21277</v>
+        <v>0.4</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>370</v>
+        <v>150</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>390</v>
+        <v>163</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 21.3% (fair +370). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -21508,12 +21508,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Indiana Fever</t>
+          <t>Connecticut Sun @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -21523,14 +21523,14 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Phoenix Mercury</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.78723</v>
+        <v>0.6</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-370</v>
+        <v>-150</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-115</v>
@@ -21557,7 +21557,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 78.7% (fair -370). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -21574,12 +21574,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Indiana Fever</t>
+          <t>Connecticut Sun @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -21589,17 +21589,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 177.5</t>
+          <t>Over 164</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.578569512662729</v>
+        <v>0.6515142147265889</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-137</v>
+        <v>-187</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-102</v>
+        <v>110</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -21623,7 +21623,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -137). Your call.</t>
+          <t>Model 65.2% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -21640,12 +21640,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Indiana Fever</t>
+          <t>Connecticut Sun @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -21655,17 +21655,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 177.5</t>
+          <t>Under 164</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.421430487337271</v>
+        <v>0.3266857852734111</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>137</v>
+        <v>206</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +137). Your call.</t>
+          <t>Model 32.7% (fair +206). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -21706,12 +21706,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Indiana Fever</t>
+          <t>Connecticut Sun @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -21721,17 +21721,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever -10.5</t>
+          <t>Phoenix Mercury -4.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.50408358982461</v>
+        <v>0.4901</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-102</v>
+        <v>104</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -21755,7 +21755,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -21772,12 +21772,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Indiana Fever</t>
+          <t>Connecticut Sun @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -21787,17 +21787,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm +10.5</t>
+          <t>Connecticut Sun +4.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.49591641017539</v>
+        <v>0.5099</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>102</v>
+        <v>-104</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -21821,7 +21821,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -21833,17 +21833,17 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Toronto Tempo</t>
+          <t>New York Liberty @ Indiana Fever</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -21853,17 +21853,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.67647</v>
+        <v>0.4686</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-209</v>
+        <v>113</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-120</v>
+        <v>-115</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 67.6% (fair -209). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -21899,17 +21899,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Toronto Tempo</t>
+          <t>New York Liberty @ Indiana Fever</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -21919,17 +21919,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.32353</v>
+        <v>0.5314</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>209</v>
+        <v>-113</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>400</v>
+        <v>117</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 32.4% (fair +209). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -21965,17 +21965,17 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Toronto Tempo</t>
+          <t>New York Liberty @ Indiana Fever</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -21985,17 +21985,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 181.5</t>
+          <t>Over 177.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5600817446466764</v>
+        <v>0.5642</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-127</v>
+        <v>-129</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -22031,17 +22031,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Toronto Tempo</t>
+          <t>New York Liberty @ Indiana Fever</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -22051,17 +22051,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 181.5</t>
+          <t>Under 177.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4399182553533236</v>
+        <v>0.4358</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -22097,17 +22097,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Toronto Tempo</t>
+          <t>New York Liberty @ Indiana Fever</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -22117,17 +22117,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Toronto Tempo +9.5</t>
+          <t>Indiana Fever +1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.6875707896599546</v>
+        <v>0.578</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-220</v>
+        <v>-137</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 68.8% (fair -220). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -22163,17 +22163,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Toronto Tempo</t>
+          <t>New York Liberty @ Indiana Fever</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -22183,17 +22183,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream -9.5</t>
+          <t>New York Liberty -1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.3124292103400454</v>
+        <v>0.422</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -22217,7 +22217,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 31.2% (fair +220). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -22229,17 +22229,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Chicago Sky</t>
+          <t>Portland Fire @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -22249,17 +22249,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks</t>
+          <t>Portland Fire</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.41237</v>
+        <v>0.07955000000000001</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>143</v>
+        <v>1157</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>125</v>
+        <v>614</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -22283,7 +22283,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 8.0% (fair +1157). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -22295,17 +22295,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Chicago Sky</t>
+          <t>Portland Fire @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -22315,17 +22315,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.58763</v>
+        <v>0.92045</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-143</v>
+        <v>-1157</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -22349,7 +22349,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 92.0% (fair -1157). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -22361,17 +22361,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Chicago Sky</t>
+          <t>Portland Fire @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -22381,17 +22381,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 183.5</t>
+          <t>Over 175.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5384</v>
+        <v>0.555</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-117</v>
+        <v>-125</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -22427,17 +22427,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Chicago Sky</t>
+          <t>Portland Fire @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -22447,14 +22447,14 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 183.5</t>
+          <t>Under 175.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4616</v>
+        <v>0.445</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>100</v>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +117). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -22493,17 +22493,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Chicago Sky</t>
+          <t>Portland Fire @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -22513,14 +22513,14 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky -2.5</t>
+          <t>Minnesota Lynx -13.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4758269718161631</v>
+        <v>0.4735</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>104</v>
@@ -22547,7 +22547,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -22559,17 +22559,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Chicago Sky</t>
+          <t>Portland Fire @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -22579,17 +22579,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks +2.5</t>
+          <t>Portland Fire +13.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5241730281838369</v>
+        <v>0.5265</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>112</v>
+        <v>-104</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -22613,7 +22613,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -22625,17 +22625,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Connecticut Sun @ Phoenix Mercury</t>
+          <t>Washington Mystics @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -22645,17 +22645,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Connecticut Sun</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4</v>
+        <v>0.21277</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>150</v>
+        <v>370</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>170</v>
+        <v>350</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -22679,7 +22679,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 21.3% (fair +370). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -22691,17 +22691,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Connecticut Sun @ Phoenix Mercury</t>
+          <t>Washington Mystics @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -22711,17 +22711,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.6</v>
+        <v>0.78723</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-150</v>
+        <v>-370</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-115</v>
+        <v>-120</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -22745,7 +22745,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 78.7% (fair -370). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -22757,17 +22757,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Connecticut Sun @ Phoenix Mercury</t>
+          <t>Washington Mystics @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -22777,17 +22777,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 163.5</t>
+          <t>Over 146.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.6623274462757939</v>
+        <v>0.6839679118943527</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-196</v>
+        <v>-216</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>102</v>
+        <v>-104</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -22811,7 +22811,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 66.2% (fair -196). Your call.</t>
+          <t>Model 68.4% (fair -216). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -22823,17 +22823,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Connecticut Sun @ Phoenix Mercury</t>
+          <t>Washington Mystics @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -22843,14 +22843,14 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 163.5</t>
+          <t>Under 146.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.3376725537242061</v>
+        <v>0.3160320881056473</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>113</v>
@@ -22877,7 +22877,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 33.8% (fair +196). Your call.</t>
+          <t>Model 31.6% (fair +216). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -22889,17 +22889,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Connecticut Sun @ Phoenix Mercury</t>
+          <t>Washington Mystics @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -22909,17 +22909,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury -4.5</t>
+          <t>Golden State Valkyries -8.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4888</v>
+        <v>0.5662870953684607</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>105</v>
+        <v>-131</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -22943,7 +22943,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -22955,17 +22955,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Connecticut Sun @ Phoenix Mercury</t>
+          <t>Washington Mystics @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -22975,17 +22975,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Connecticut Sun +4.5</t>
+          <t>Washington Mystics +8.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5112</v>
+        <v>0.4337129046315393</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-105</v>
+        <v>131</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-102</v>
+        <v>113</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -23009,7 +23009,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -23018,1197 +23018,9 @@
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>New York Liberty @ Indiana Fever</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>0.4703000000000001</v>
-      </c>
-      <c r="G29" s="14" t="n">
-        <v>113</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>-115</v>
-      </c>
-      <c r="I29" s="13">
-        <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
-        <v/>
-      </c>
-      <c r="J29" s="16">
-        <f>IF($H$29="","",$F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))</f>
-        <v/>
-      </c>
-      <c r="K29" s="17">
-        <f>IF($H$29="","",MAX(0,($F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))/IF($H$29&lt;0,-100/$H$29,$H$29/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L29" s="18">
-        <f>IF($H$29="","",ROUND(MIN($K$29,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M29" s="12">
-        <f>IF($J$29="","",IF($J$29&lt;0,"Pass",IF($J$29&lt;'Settings'!$B$4,"Thin",IF($J$29&lt;0.06,"✅ Sharp band",IF($J$29&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N29" s="19" t="inlineStr">
-        <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
-        </is>
-      </c>
-      <c r="O29" s="15" t="n"/>
-      <c r="P29" s="16">
-        <f>IF(OR($H$29="",$O$29=""),"",(1+IF($H$29&lt;0,-100/$H$29,$H$29/100))/(1+IF($O$29&lt;0,-100/$O$29,$O$29/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>New York Liberty @ Indiana Fever</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="inlineStr">
-        <is>
-          <t>Indiana Fever</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>0.5296999999999999</v>
-      </c>
-      <c r="G30" s="14" t="n">
-        <v>-113</v>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="I30" s="13">
-        <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
-        <v/>
-      </c>
-      <c r="J30" s="16">
-        <f>IF($H$30="","",$F$30*IF($H$30&lt;0,-100/$H$30,$H$30/100)-(1-$F$30))</f>
-        <v/>
-      </c>
-      <c r="K30" s="17">
-        <f>IF($H$30="","",MAX(0,($F$30*IF($H$30&lt;0,-100/$H$30,$H$30/100)-(1-$F$30))/IF($H$30&lt;0,-100/$H$30,$H$30/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L30" s="18">
-        <f>IF($H$30="","",ROUND(MIN($K$30,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M30" s="12">
-        <f>IF($J$30="","",IF($J$30&lt;0,"Pass",IF($J$30&lt;'Settings'!$B$4,"Thin",IF($J$30&lt;0.06,"✅ Sharp band",IF($J$30&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N30" s="19" t="inlineStr">
-        <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
-        </is>
-      </c>
-      <c r="O30" s="15" t="n"/>
-      <c r="P30" s="16">
-        <f>IF(OR($H$30="",$O$30=""),"",(1+IF($H$30&lt;0,-100/$H$30,$H$30/100))/(1+IF($O$30&lt;0,-100/$O$30,$O$30/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>New York Liberty @ Indiana Fever</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>Over 175.5</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>0.6766082971414675</v>
-      </c>
-      <c r="G31" s="14" t="n">
-        <v>-209</v>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>-104</v>
-      </c>
-      <c r="I31" s="13">
-        <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
-        <v/>
-      </c>
-      <c r="J31" s="16">
-        <f>IF($H$31="","",$F$31*IF($H$31&lt;0,-100/$H$31,$H$31/100)-(1-$F$31))</f>
-        <v/>
-      </c>
-      <c r="K31" s="17">
-        <f>IF($H$31="","",MAX(0,($F$31*IF($H$31&lt;0,-100/$H$31,$H$31/100)-(1-$F$31))/IF($H$31&lt;0,-100/$H$31,$H$31/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L31" s="18">
-        <f>IF($H$31="","",ROUND(MIN($K$31,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M31" s="12">
-        <f>IF($J$31="","",IF($J$31&lt;0,"Pass",IF($J$31&lt;'Settings'!$B$4,"Thin",IF($J$31&lt;0.06,"✅ Sharp band",IF($J$31&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N31" s="19" t="inlineStr">
-        <is>
-          <t>Model 67.7% (fair -209). Your call.</t>
-        </is>
-      </c>
-      <c r="O31" s="15" t="n"/>
-      <c r="P31" s="16">
-        <f>IF(OR($H$31="",$O$31=""),"",(1+IF($H$31&lt;0,-100/$H$31,$H$31/100))/(1+IF($O$31&lt;0,-100/$O$31,$O$31/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>New York Liberty @ Indiana Fever</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E32" s="20" t="inlineStr">
-        <is>
-          <t>Under 175.5</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>0.3233917028585325</v>
-      </c>
-      <c r="G32" s="14" t="n">
-        <v>209</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>113</v>
-      </c>
-      <c r="I32" s="13">
-        <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
-        <v/>
-      </c>
-      <c r="J32" s="16">
-        <f>IF($H$32="","",$F$32*IF($H$32&lt;0,-100/$H$32,$H$32/100)-(1-$F$32))</f>
-        <v/>
-      </c>
-      <c r="K32" s="17">
-        <f>IF($H$32="","",MAX(0,($F$32*IF($H$32&lt;0,-100/$H$32,$H$32/100)-(1-$F$32))/IF($H$32&lt;0,-100/$H$32,$H$32/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L32" s="18">
-        <f>IF($H$32="","",ROUND(MIN($K$32,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M32" s="12">
-        <f>IF($J$32="","",IF($J$32&lt;0,"Pass",IF($J$32&lt;'Settings'!$B$4,"Thin",IF($J$32&lt;0.06,"✅ Sharp band",IF($J$32&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N32" s="19" t="inlineStr">
-        <is>
-          <t>Model 32.3% (fair +209). Your call.</t>
-        </is>
-      </c>
-      <c r="O32" s="15" t="n"/>
-      <c r="P32" s="16">
-        <f>IF(OR($H$32="",$O$32=""),"",(1+IF($H$32&lt;0,-100/$H$32,$H$32/100))/(1+IF($O$32&lt;0,-100/$O$32,$O$32/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>New York Liberty @ Indiana Fever</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>Indiana Fever +1.5</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>0.5725</v>
-      </c>
-      <c r="G33" s="14" t="n">
-        <v>-134</v>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>108</v>
-      </c>
-      <c r="I33" s="13">
-        <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
-        <v/>
-      </c>
-      <c r="J33" s="16">
-        <f>IF($H$33="","",$F$33*IF($H$33&lt;0,-100/$H$33,$H$33/100)-(1-$F$33))</f>
-        <v/>
-      </c>
-      <c r="K33" s="17">
-        <f>IF($H$33="","",MAX(0,($F$33*IF($H$33&lt;0,-100/$H$33,$H$33/100)-(1-$F$33))/IF($H$33&lt;0,-100/$H$33,$H$33/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L33" s="18">
-        <f>IF($H$33="","",ROUND(MIN($K$33,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M33" s="12">
-        <f>IF($J$33="","",IF($J$33&lt;0,"Pass",IF($J$33&lt;'Settings'!$B$4,"Thin",IF($J$33&lt;0.06,"✅ Sharp band",IF($J$33&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N33" s="19" t="inlineStr">
-        <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
-        </is>
-      </c>
-      <c r="O33" s="15" t="n"/>
-      <c r="P33" s="16">
-        <f>IF(OR($H$33="",$O$33=""),"",(1+IF($H$33&lt;0,-100/$H$33,$H$33/100))/(1+IF($O$33&lt;0,-100/$O$33,$O$33/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>New York Liberty @ Indiana Fever</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>New York Liberty -1.5</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>0.4275</v>
-      </c>
-      <c r="G34" s="14" t="n">
-        <v>134</v>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>-105</v>
-      </c>
-      <c r="I34" s="13">
-        <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
-        <v/>
-      </c>
-      <c r="J34" s="16">
-        <f>IF($H$34="","",$F$34*IF($H$34&lt;0,-100/$H$34,$H$34/100)-(1-$F$34))</f>
-        <v/>
-      </c>
-      <c r="K34" s="17">
-        <f>IF($H$34="","",MAX(0,($F$34*IF($H$34&lt;0,-100/$H$34,$H$34/100)-(1-$F$34))/IF($H$34&lt;0,-100/$H$34,$H$34/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L34" s="18">
-        <f>IF($H$34="","",ROUND(MIN($K$34,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M34" s="12">
-        <f>IF($J$34="","",IF($J$34&lt;0,"Pass",IF($J$34&lt;'Settings'!$B$4,"Thin",IF($J$34&lt;0.06,"✅ Sharp band",IF($J$34&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N34" s="19" t="inlineStr">
-        <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
-        </is>
-      </c>
-      <c r="O34" s="15" t="n"/>
-      <c r="P34" s="16">
-        <f>IF(OR($H$34="",$O$34=""),"",(1+IF($H$34&lt;0,-100/$H$34,$H$34/100))/(1+IF($O$34&lt;0,-100/$O$34,$O$34/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Portland Fire @ Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>Portland Fire</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>0.07955000000000001</v>
-      </c>
-      <c r="G35" s="14" t="n">
-        <v>1157</v>
-      </c>
-      <c r="H35" s="15" t="n">
-        <v>650</v>
-      </c>
-      <c r="I35" s="13">
-        <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
-        <v/>
-      </c>
-      <c r="J35" s="16">
-        <f>IF($H$35="","",$F$35*IF($H$35&lt;0,-100/$H$35,$H$35/100)-(1-$F$35))</f>
-        <v/>
-      </c>
-      <c r="K35" s="17">
-        <f>IF($H$35="","",MAX(0,($F$35*IF($H$35&lt;0,-100/$H$35,$H$35/100)-(1-$F$35))/IF($H$35&lt;0,-100/$H$35,$H$35/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L35" s="18">
-        <f>IF($H$35="","",ROUND(MIN($K$35,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M35" s="12">
-        <f>IF($J$35="","",IF($J$35&lt;0,"Pass",IF($J$35&lt;'Settings'!$B$4,"Thin",IF($J$35&lt;0.06,"✅ Sharp band",IF($J$35&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N35" s="19" t="inlineStr">
-        <is>
-          <t>Model 8.0% (fair +1157). Your call.</t>
-        </is>
-      </c>
-      <c r="O35" s="15" t="n"/>
-      <c r="P35" s="16">
-        <f>IF(OR($H$35="",$O$35=""),"",(1+IF($H$35&lt;0,-100/$H$35,$H$35/100))/(1+IF($O$35&lt;0,-100/$O$35,$O$35/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>Portland Fire @ Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="C36" s="20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="D36" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E36" s="20" t="inlineStr">
-        <is>
-          <t>Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>0.92045</v>
-      </c>
-      <c r="G36" s="14" t="n">
-        <v>-1157</v>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>-115</v>
-      </c>
-      <c r="I36" s="13">
-        <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
-        <v/>
-      </c>
-      <c r="J36" s="16">
-        <f>IF($H$36="","",$F$36*IF($H$36&lt;0,-100/$H$36,$H$36/100)-(1-$F$36))</f>
-        <v/>
-      </c>
-      <c r="K36" s="17">
-        <f>IF($H$36="","",MAX(0,($F$36*IF($H$36&lt;0,-100/$H$36,$H$36/100)-(1-$F$36))/IF($H$36&lt;0,-100/$H$36,$H$36/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L36" s="18">
-        <f>IF($H$36="","",ROUND(MIN($K$36,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M36" s="12">
-        <f>IF($J$36="","",IF($J$36&lt;0,"Pass",IF($J$36&lt;'Settings'!$B$4,"Thin",IF($J$36&lt;0.06,"✅ Sharp band",IF($J$36&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N36" s="19" t="inlineStr">
-        <is>
-          <t>Model 92.0% (fair -1157). Your call.</t>
-        </is>
-      </c>
-      <c r="O36" s="15" t="n"/>
-      <c r="P36" s="16">
-        <f>IF(OR($H$36="",$O$36=""),"",(1+IF($H$36&lt;0,-100/$H$36,$H$36/100))/(1+IF($O$36&lt;0,-100/$O$36,$O$36/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>Portland Fire @ Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Over 175.5</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>0.5574</v>
-      </c>
-      <c r="G37" s="14" t="n">
-        <v>-126</v>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" s="13">
-        <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
-        <v/>
-      </c>
-      <c r="J37" s="16">
-        <f>IF($H$37="","",$F$37*IF($H$37&lt;0,-100/$H$37,$H$37/100)-(1-$F$37))</f>
-        <v/>
-      </c>
-      <c r="K37" s="17">
-        <f>IF($H$37="","",MAX(0,($F$37*IF($H$37&lt;0,-100/$H$37,$H$37/100)-(1-$F$37))/IF($H$37&lt;0,-100/$H$37,$H$37/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L37" s="18">
-        <f>IF($H$37="","",ROUND(MIN($K$37,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M37" s="12">
-        <f>IF($J$37="","",IF($J$37&lt;0,"Pass",IF($J$37&lt;'Settings'!$B$4,"Thin",IF($J$37&lt;0.06,"✅ Sharp band",IF($J$37&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N37" s="19" t="inlineStr">
-        <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
-        </is>
-      </c>
-      <c r="O37" s="15" t="n"/>
-      <c r="P37" s="16">
-        <f>IF(OR($H$37="",$O$37=""),"",(1+IF($H$37&lt;0,-100/$H$37,$H$37/100))/(1+IF($O$37&lt;0,-100/$O$37,$O$37/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>Portland Fire @ Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E38" s="20" t="inlineStr">
-        <is>
-          <t>Under 175.5</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>0.4426</v>
-      </c>
-      <c r="G38" s="14" t="n">
-        <v>126</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>-104</v>
-      </c>
-      <c r="I38" s="13">
-        <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
-        <v/>
-      </c>
-      <c r="J38" s="16">
-        <f>IF($H$38="","",$F$38*IF($H$38&lt;0,-100/$H$38,$H$38/100)-(1-$F$38))</f>
-        <v/>
-      </c>
-      <c r="K38" s="17">
-        <f>IF($H$38="","",MAX(0,($F$38*IF($H$38&lt;0,-100/$H$38,$H$38/100)-(1-$F$38))/IF($H$38&lt;0,-100/$H$38,$H$38/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L38" s="18">
-        <f>IF($H$38="","",ROUND(MIN($K$38,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M38" s="12">
-        <f>IF($J$38="","",IF($J$38&lt;0,"Pass",IF($J$38&lt;'Settings'!$B$4,"Thin",IF($J$38&lt;0.06,"✅ Sharp band",IF($J$38&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N38" s="19" t="inlineStr">
-        <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
-        </is>
-      </c>
-      <c r="O38" s="15" t="n"/>
-      <c r="P38" s="16">
-        <f>IF(OR($H$38="",$O$38=""),"",(1+IF($H$38&lt;0,-100/$H$38,$H$38/100))/(1+IF($O$38&lt;0,-100/$O$38,$O$38/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>Portland Fire @ Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>Minnesota Lynx -13.5</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>0.4735</v>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>111</v>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>104</v>
-      </c>
-      <c r="I39" s="13">
-        <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
-        <v/>
-      </c>
-      <c r="J39" s="16">
-        <f>IF($H$39="","",$F$39*IF($H$39&lt;0,-100/$H$39,$H$39/100)-(1-$F$39))</f>
-        <v/>
-      </c>
-      <c r="K39" s="17">
-        <f>IF($H$39="","",MAX(0,($F$39*IF($H$39&lt;0,-100/$H$39,$H$39/100)-(1-$F$39))/IF($H$39&lt;0,-100/$H$39,$H$39/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L39" s="18">
-        <f>IF($H$39="","",ROUND(MIN($K$39,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M39" s="12">
-        <f>IF($J$39="","",IF($J$39&lt;0,"Pass",IF($J$39&lt;'Settings'!$B$4,"Thin",IF($J$39&lt;0.06,"✅ Sharp band",IF($J$39&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N39" s="19" t="inlineStr">
-        <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
-        </is>
-      </c>
-      <c r="O39" s="15" t="n"/>
-      <c r="P39" s="16">
-        <f>IF(OR($H$39="",$O$39=""),"",(1+IF($H$39&lt;0,-100/$H$39,$H$39/100))/(1+IF($O$39&lt;0,-100/$O$39,$O$39/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>Portland Fire @ Minnesota Lynx</t>
-        </is>
-      </c>
-      <c r="C40" s="20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E40" s="20" t="inlineStr">
-        <is>
-          <t>Portland Fire +13.5</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>0.5265</v>
-      </c>
-      <c r="G40" s="14" t="n">
-        <v>-111</v>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>-104</v>
-      </c>
-      <c r="I40" s="13">
-        <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
-        <v/>
-      </c>
-      <c r="J40" s="16">
-        <f>IF($H$40="","",$F$40*IF($H$40&lt;0,-100/$H$40,$H$40/100)-(1-$F$40))</f>
-        <v/>
-      </c>
-      <c r="K40" s="17">
-        <f>IF($H$40="","",MAX(0,($F$40*IF($H$40&lt;0,-100/$H$40,$H$40/100)-(1-$F$40))/IF($H$40&lt;0,-100/$H$40,$H$40/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L40" s="18">
-        <f>IF($H$40="","",ROUND(MIN($K$40,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M40" s="12">
-        <f>IF($J$40="","",IF($J$40&lt;0,"Pass",IF($J$40&lt;'Settings'!$B$4,"Thin",IF($J$40&lt;0.06,"✅ Sharp band",IF($J$40&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N40" s="19" t="inlineStr">
-        <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
-        </is>
-      </c>
-      <c r="O40" s="15" t="n"/>
-      <c r="P40" s="16">
-        <f>IF(OR($H$40="",$O$40=""),"",(1+IF($H$40&lt;0,-100/$H$40,$H$40/100))/(1+IF($O$40&lt;0,-100/$O$40,$O$40/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>Washington Mystics @ Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>Washington Mystics</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>0.21277</v>
-      </c>
-      <c r="G41" s="14" t="n">
-        <v>370</v>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>350</v>
-      </c>
-      <c r="I41" s="13">
-        <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
-        <v/>
-      </c>
-      <c r="J41" s="16">
-        <f>IF($H$41="","",$F$41*IF($H$41&lt;0,-100/$H$41,$H$41/100)-(1-$F$41))</f>
-        <v/>
-      </c>
-      <c r="K41" s="17">
-        <f>IF($H$41="","",MAX(0,($F$41*IF($H$41&lt;0,-100/$H$41,$H$41/100)-(1-$F$41))/IF($H$41&lt;0,-100/$H$41,$H$41/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L41" s="18">
-        <f>IF($H$41="","",ROUND(MIN($K$41,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M41" s="12">
-        <f>IF($J$41="","",IF($J$41&lt;0,"Pass",IF($J$41&lt;'Settings'!$B$4,"Thin",IF($J$41&lt;0.06,"✅ Sharp band",IF($J$41&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N41" s="19" t="inlineStr">
-        <is>
-          <t>Model 21.3% (fair +370). Your call.</t>
-        </is>
-      </c>
-      <c r="O41" s="15" t="n"/>
-      <c r="P41" s="16">
-        <f>IF(OR($H$41="",$O$41=""),"",(1+IF($H$41&lt;0,-100/$H$41,$H$41/100))/(1+IF($O$41&lt;0,-100/$O$41,$O$41/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="inlineStr">
-        <is>
-          <t>Washington Mystics @ Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="C42" s="20" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E42" s="20" t="inlineStr">
-        <is>
-          <t>Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>0.78723</v>
-      </c>
-      <c r="G42" s="14" t="n">
-        <v>-370</v>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>-115</v>
-      </c>
-      <c r="I42" s="13">
-        <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
-        <v/>
-      </c>
-      <c r="J42" s="16">
-        <f>IF($H$42="","",$F$42*IF($H$42&lt;0,-100/$H$42,$H$42/100)-(1-$F$42))</f>
-        <v/>
-      </c>
-      <c r="K42" s="17">
-        <f>IF($H$42="","",MAX(0,($F$42*IF($H$42&lt;0,-100/$H$42,$H$42/100)-(1-$F$42))/IF($H$42&lt;0,-100/$H$42,$H$42/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L42" s="18">
-        <f>IF($H$42="","",ROUND(MIN($K$42,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M42" s="12">
-        <f>IF($J$42="","",IF($J$42&lt;0,"Pass",IF($J$42&lt;'Settings'!$B$4,"Thin",IF($J$42&lt;0.06,"✅ Sharp band",IF($J$42&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N42" s="19" t="inlineStr">
-        <is>
-          <t>Model 78.7% (fair -370). Your call.</t>
-        </is>
-      </c>
-      <c r="O42" s="15" t="n"/>
-      <c r="P42" s="16">
-        <f>IF(OR($H$42="",$O$42=""),"",(1+IF($H$42&lt;0,-100/$H$42,$H$42/100))/(1+IF($O$42&lt;0,-100/$O$42,$O$42/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>Washington Mystics @ Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Over 149.5</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="n">
-        <v>0.618808487807622</v>
-      </c>
-      <c r="G43" s="14" t="n">
-        <v>-162</v>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>111</v>
-      </c>
-      <c r="I43" s="13">
-        <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
-        <v/>
-      </c>
-      <c r="J43" s="16">
-        <f>IF($H$43="","",$F$43*IF($H$43&lt;0,-100/$H$43,$H$43/100)-(1-$F$43))</f>
-        <v/>
-      </c>
-      <c r="K43" s="17">
-        <f>IF($H$43="","",MAX(0,($F$43*IF($H$43&lt;0,-100/$H$43,$H$43/100)-(1-$F$43))/IF($H$43&lt;0,-100/$H$43,$H$43/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L43" s="18">
-        <f>IF($H$43="","",ROUND(MIN($K$43,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M43" s="12">
-        <f>IF($J$43="","",IF($J$43&lt;0,"Pass",IF($J$43&lt;'Settings'!$B$4,"Thin",IF($J$43&lt;0.06,"✅ Sharp band",IF($J$43&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N43" s="19" t="inlineStr">
-        <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
-        </is>
-      </c>
-      <c r="O43" s="15" t="n"/>
-      <c r="P43" s="16">
-        <f>IF(OR($H$43="",$O$43=""),"",(1+IF($H$43&lt;0,-100/$H$43,$H$43/100))/(1+IF($O$43&lt;0,-100/$O$43,$O$43/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="inlineStr">
-        <is>
-          <t>Washington Mystics @ Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E44" s="20" t="inlineStr">
-        <is>
-          <t>Under 149.5</t>
-        </is>
-      </c>
-      <c r="F44" s="13" t="n">
-        <v>0.381191512192378</v>
-      </c>
-      <c r="G44" s="14" t="n">
-        <v>162</v>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>108</v>
-      </c>
-      <c r="I44" s="13">
-        <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
-        <v/>
-      </c>
-      <c r="J44" s="16">
-        <f>IF($H$44="","",$F$44*IF($H$44&lt;0,-100/$H$44,$H$44/100)-(1-$F$44))</f>
-        <v/>
-      </c>
-      <c r="K44" s="17">
-        <f>IF($H$44="","",MAX(0,($F$44*IF($H$44&lt;0,-100/$H$44,$H$44/100)-(1-$F$44))/IF($H$44&lt;0,-100/$H$44,$H$44/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L44" s="18">
-        <f>IF($H$44="","",ROUND(MIN($K$44,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M44" s="12">
-        <f>IF($J$44="","",IF($J$44&lt;0,"Pass",IF($J$44&lt;'Settings'!$B$4,"Thin",IF($J$44&lt;0.06,"✅ Sharp band",IF($J$44&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N44" s="19" t="inlineStr">
-        <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
-        </is>
-      </c>
-      <c r="O44" s="15" t="n"/>
-      <c r="P44" s="16">
-        <f>IF(OR($H$44="",$O$44=""),"",(1+IF($H$44&lt;0,-100/$H$44,$H$44/100))/(1+IF($O$44&lt;0,-100/$O$44,$O$44/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>Washington Mystics @ Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>Golden State Valkyries -8.5</t>
-        </is>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>0.544</v>
-      </c>
-      <c r="G45" s="14" t="n">
-        <v>-119</v>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>-105</v>
-      </c>
-      <c r="I45" s="13">
-        <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
-        <v/>
-      </c>
-      <c r="J45" s="16">
-        <f>IF($H$45="","",$F$45*IF($H$45&lt;0,-100/$H$45,$H$45/100)-(1-$F$45))</f>
-        <v/>
-      </c>
-      <c r="K45" s="17">
-        <f>IF($H$45="","",MAX(0,($F$45*IF($H$45&lt;0,-100/$H$45,$H$45/100)-(1-$F$45))/IF($H$45&lt;0,-100/$H$45,$H$45/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L45" s="18">
-        <f>IF($H$45="","",ROUND(MIN($K$45,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M45" s="12">
-        <f>IF($J$45="","",IF($J$45&lt;0,"Pass",IF($J$45&lt;'Settings'!$B$4,"Thin",IF($J$45&lt;0.06,"✅ Sharp band",IF($J$45&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N45" s="19" t="inlineStr">
-        <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
-        </is>
-      </c>
-      <c r="O45" s="15" t="n"/>
-      <c r="P45" s="16">
-        <f>IF(OR($H$45="",$O$45=""),"",(1+IF($H$45&lt;0,-100/$H$45,$H$45/100))/(1+IF($O$45&lt;0,-100/$O$45,$O$45/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="inlineStr">
-        <is>
-          <t>Washington Mystics @ Golden State Valkyries</t>
-        </is>
-      </c>
-      <c r="C46" s="20" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E46" s="20" t="inlineStr">
-        <is>
-          <t>Washington Mystics +8.5</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="G46" s="14" t="n">
-        <v>119</v>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>113</v>
-      </c>
-      <c r="I46" s="13">
-        <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
-        <v/>
-      </c>
-      <c r="J46" s="16">
-        <f>IF($H$46="","",$F$46*IF($H$46&lt;0,-100/$H$46,$H$46/100)-(1-$F$46))</f>
-        <v/>
-      </c>
-      <c r="K46" s="17">
-        <f>IF($H$46="","",MAX(0,($F$46*IF($H$46&lt;0,-100/$H$46,$H$46/100)-(1-$F$46))/IF($H$46&lt;0,-100/$H$46,$H$46/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L46" s="18">
-        <f>IF($H$46="","",ROUND(MIN($K$46,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M46" s="12">
-        <f>IF($J$46="","",IF($J$46&lt;0,"Pass",IF($J$46&lt;'Settings'!$B$4,"Thin",IF($J$46&lt;0.06,"✅ Sharp band",IF($J$46&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N46" s="19" t="inlineStr">
-        <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
-        </is>
-      </c>
-      <c r="O46" s="15" t="n"/>
-      <c r="P46" s="16">
-        <f>IF(OR($H$46="",$O$46=""),"",(1+IF($H$46&lt;0,-100/$H$46,$H$46/100))/(1+IF($O$46&lt;0,-100/$O$46,$O$46/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J46">
+  <conditionalFormatting sqref="J5:J28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -24230,7 +23042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -24355,12 +23167,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Atlanta United FC @ Nashville SC</t>
+          <t>LAFC @ LA Galaxy</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>02:25</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -24370,7 +23182,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>LAFC</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
@@ -24379,9 +23191,7 @@
       <c r="G5" s="14" t="n">
         <v>243</v>
       </c>
-      <c r="H5" s="15" t="n">
-        <v>480</v>
-      </c>
+      <c r="H5" s="15" t="n"/>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
         <v/>
@@ -24421,12 +23231,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Atlanta United FC @ Nashville SC</t>
+          <t>LAFC @ LA Galaxy</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>02:25</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -24436,7 +23246,7 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
@@ -24445,9 +23255,7 @@
       <c r="G6" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="H6" s="15" t="n">
-        <v>-162</v>
-      </c>
+      <c r="H6" s="15" t="n"/>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
         <v/>
@@ -24479,137 +23287,9 @@
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>LAFC @ LA Galaxy</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>02:25</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>LAFC</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>0.2919</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>243</v>
-      </c>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="13">
-        <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
-        <v/>
-      </c>
-      <c r="J7" s="16">
-        <f>IF($H$7="","",$F$7*IF($H$7&lt;0,-100/$H$7,$H$7/100)-(1-$F$7))</f>
-        <v/>
-      </c>
-      <c r="K7" s="17">
-        <f>IF($H$7="","",MAX(0,($F$7*IF($H$7&lt;0,-100/$H$7,$H$7/100)-(1-$F$7))/IF($H$7&lt;0,-100/$H$7,$H$7/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L7" s="18">
-        <f>IF($H$7="","",ROUND(MIN($K$7,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M7" s="12">
-        <f>IF($J$7="","",IF($J$7&lt;0,"Pass",IF($J$7&lt;'Settings'!$B$4,"Thin",IF($J$7&lt;0.06,"✅ Sharp band",IF($J$7&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N7" s="19" t="inlineStr">
-        <is>
-          <t>Model 29.2% (fair +243). Your call.</t>
-        </is>
-      </c>
-      <c r="O7" s="15" t="n"/>
-      <c r="P7" s="16">
-        <f>IF(OR($H$7="",$O$7=""),"",(1+IF($H$7&lt;0,-100/$H$7,$H$7/100))/(1+IF($O$7&lt;0,-100/$O$7,$O$7/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>LAFC @ LA Galaxy</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>02:25</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>0.4342</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <v>130</v>
-      </c>
-      <c r="H8" s="15" t="n"/>
-      <c r="I8" s="13">
-        <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
-        <v/>
-      </c>
-      <c r="J8" s="16">
-        <f>IF($H$8="","",$F$8*IF($H$8&lt;0,-100/$H$8,$H$8/100)-(1-$F$8))</f>
-        <v/>
-      </c>
-      <c r="K8" s="17">
-        <f>IF($H$8="","",MAX(0,($F$8*IF($H$8&lt;0,-100/$H$8,$H$8/100)-(1-$F$8))/IF($H$8&lt;0,-100/$H$8,$H$8/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L8" s="18">
-        <f>IF($H$8="","",ROUND(MIN($K$8,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M8" s="12">
-        <f>IF($J$8="","",IF($J$8&lt;0,"Pass",IF($J$8&lt;'Settings'!$B$4,"Thin",IF($J$8&lt;0.06,"✅ Sharp band",IF($J$8&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N8" s="19" t="inlineStr">
-        <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
-        </is>
-      </c>
-      <c r="O8" s="15" t="n"/>
-      <c r="P8" s="16">
-        <f>IF(OR($H$8="",$O$8=""),"",(1+IF($H$8&lt;0,-100/$H$8,$H$8/100))/(1+IF($O$8&lt;0,-100/$O$8,$O$8/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J8">
+  <conditionalFormatting sqref="J5:J6">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -24713,28 +23393,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>0.2487</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.393</v>
+        <v>0.3943</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-87.92</v>
+        <v>-87.25</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-14.04</v>
+        <v>-13.76</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5421</v>
+        <v>0.5438</v>
       </c>
     </row>
     <row r="6">
@@ -24744,28 +23424,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2495</v>
+        <v>0.2494</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.3874</v>
+        <v>0.389</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-86.64</v>
+        <v>-85.95999999999999</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-15.61</v>
+        <v>-15.27</v>
       </c>
       <c r="H6" s="24" t="n">
         <v>6</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5605</v>
+        <v>0.5622</v>
       </c>
     </row>
     <row r="7">
@@ -24848,7 +23528,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=423, ECE 0.044 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=426, ECE 0.045 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -24962,16 +23642,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5434</v>
+        <v>0.5433</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5401</v>
+        <v>0.5344</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0033</v>
+        <v>-0.0089</v>
       </c>
     </row>
     <row r="22">
@@ -24981,16 +23661,16 @@
         </is>
       </c>
       <c r="B22" s="21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>0.6401</v>
+        <v>0.6395</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>0.5417</v>
+        <v>0.551</v>
       </c>
       <c r="E22" s="27" t="n">
-        <v>-0.0985</v>
+        <v>-0.08840000000000001</v>
       </c>
     </row>
     <row r="23">
